--- a/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,3; 57,77</t>
+          <t>28,52; 56,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 28,91</t>
+          <t>-1,76; 29,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,73; -4,78</t>
+          <t>-43,38; -7,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,63; 58,59</t>
+          <t>26,85; 56,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,94; 49,61</t>
+          <t>19,1; 49,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,3; -18,8</t>
+          <t>-43,69; -20,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,11; 53,26</t>
+          <t>31,36; 52,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,42; 37,06</t>
+          <t>14,24; 36,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-40,13; -17,84</t>
+          <t>-40,23; -16,86</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,58; 154,33</t>
+          <t>52,02; 152,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 75,04</t>
+          <t>-3,63; 73,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,51; -6,12</t>
+          <t>-81,08; -5,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,09; 196,81</t>
+          <t>53,32; 179,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,76; 160,25</t>
+          <t>37,87; 150,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,95; -55,91</t>
+          <t>-88,41; -59,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,28; 139,83</t>
+          <t>63,17; 141,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,88; 98,16</t>
+          <t>28,54; 96,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,99; -41,04</t>
+          <t>-81,12; -38,99</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,71; 55,76</t>
+          <t>28,27; 55,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 15,39</t>
+          <t>-9,76; 16,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-30,02; -5,36</t>
+          <t>-28,02; -5,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,55; 69,4</t>
+          <t>45,56; 69,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 30,96</t>
+          <t>6,3; 31,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 10,36</t>
+          <t>-10,2; 10,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,36; 59,0</t>
+          <t>40,71; 58,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 18,66</t>
+          <t>0,67; 18,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -0,06</t>
+          <t>-16,99; -0,04</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,88; 254,79</t>
+          <t>74,52; 238,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 66,39</t>
+          <t>-27,21; 68,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,45; -23,88</t>
+          <t>-77,19; -24,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>163,7; 492,59</t>
+          <t>159,35; 479,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,63; 191,15</t>
+          <t>20,86; 211,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 65,04</t>
+          <t>-38,77; 71,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>132,04; 276,23</t>
+          <t>129,97; 276,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 87,08</t>
+          <t>2,37; 88,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -1,53</t>
+          <t>-55,08; -1,63</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,56; 62,92</t>
+          <t>34,95; 62,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 28,89</t>
+          <t>-1,27; 27,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,49; -0,59</t>
+          <t>-24,97; -0,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,39; 61,31</t>
+          <t>37,02; 61,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 25,82</t>
+          <t>0,5; 26,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 3,01</t>
+          <t>-18,65; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,31; 58,55</t>
+          <t>40,42; 58,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 23,99</t>
+          <t>4,86; 24,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,59; -2,45</t>
+          <t>-18,25; -2,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96,66; 292,19</t>
+          <t>91,73; 279,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 127,46</t>
+          <t>-4,16; 117,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,89; -0,87</t>
+          <t>-69,29; -0,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113,71; 335,79</t>
+          <t>113,49; 337,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 127,42</t>
+          <t>0,91; 136,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,22; 17,75</t>
+          <t>-60,33; 11,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>118,5; 261,32</t>
+          <t>119,44; 254,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,65; 102,83</t>
+          <t>15,23; 106,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,79; -7,59</t>
+          <t>-57,61; -9,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55,92; 76,15</t>
+          <t>56,72; 76,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,54; 57,39</t>
+          <t>30,03; 56,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 16,78</t>
+          <t>-10,77; 17,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,04; 75,07</t>
+          <t>56,92; 76,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>36,82; 61,29</t>
+          <t>35,95; 61,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 44,92</t>
+          <t>4,87; 43,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,34; 73,71</t>
+          <t>60,22; 73,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,88; 57,24</t>
+          <t>37,31; 55,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 26,8</t>
+          <t>2,03; 27,22</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>134,61; 344,92</t>
+          <t>140,15; 350,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80,5; 261,68</t>
+          <t>79,65; 247,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 69,06</t>
+          <t>-28,81; 72,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>145,94; 339,12</t>
+          <t>154,09; 377,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>103,43; 263,11</t>
+          <t>100,69; 285,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,76; 186,65</t>
+          <t>12,63; 184,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>160,44; 301,87</t>
+          <t>164,44; 302,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>106,27; 228,37</t>
+          <t>105,37; 222,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,16; 103,69</t>
+          <t>5,21; 103,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,61; 75,4</t>
+          <t>15,32; 73,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,2; 85,74</t>
+          <t>35,69; 85,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 15,15</t>
+          <t>-35,71; 15,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33,5; 82,45</t>
+          <t>34,4; 82,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41,4; 87,3</t>
+          <t>38,29; 87,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 26,1</t>
+          <t>-23,26; 26,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,25; 74,01</t>
+          <t>37,04; 74,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46,31; 81,2</t>
+          <t>45,84; 81,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 16,15</t>
+          <t>-23,15; 12,71</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,62; 568,08</t>
+          <t>25,48; 533,29</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55,89; 634,54</t>
+          <t>57,55; 642,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 122,63</t>
+          <t>-66,27; 132,33</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60,02; 674,97</t>
+          <t>63,28; 688,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,17; 724,45</t>
+          <t>68,37; 706,09</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 240,55</t>
+          <t>-47,67; 200,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,77; 490,15</t>
+          <t>77,89; 462,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>89,82; 501,94</t>
+          <t>87,32; 503,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 107,64</t>
+          <t>-47,94; 67,74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>34,24; 64,14</t>
+          <t>36,01; 64,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>22,33; 57,48</t>
+          <t>20,16; 57,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 24,36</t>
+          <t>-2,85; 24,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36,59; 64,17</t>
+          <t>37,41; 63,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>32,5; 64,12</t>
+          <t>30,18; 63,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,31; 27,02</t>
+          <t>-0,47; 28,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,37; 59,49</t>
+          <t>39,7; 60,45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>32,71; 56,8</t>
+          <t>33,9; 57,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 21,97</t>
+          <t>1,74; 21,57</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>112,61; 453,28</t>
+          <t>123,84; 489,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>70,68; 387,05</t>
+          <t>72,36; 384,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 166,28</t>
+          <t>-9,86; 172,21</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>104,28; 327,97</t>
+          <t>103,01; 316,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>90,22; 325,18</t>
+          <t>85,11; 319,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 132,03</t>
+          <t>-5,69; 128,92</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>127,45; 305,29</t>
+          <t>123,2; 302,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>103,71; 279,53</t>
+          <t>113,24; 293,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,36; 110,1</t>
+          <t>5,46; 108,94</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>41,38; 59,87</t>
+          <t>40,42; 59,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>25,94; 46,33</t>
+          <t>27,25; 46,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,18; -9,3</t>
+          <t>-24,67; -8,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37,1; 56,48</t>
+          <t>37,58; 56,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,54; 41,52</t>
+          <t>21,25; 40,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-31,68; -14,39</t>
+          <t>-31,4; -15,01</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,48; 55,64</t>
+          <t>41,91; 55,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>26,65; 41,18</t>
+          <t>27,64; 41,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-25,78; -13,87</t>
+          <t>-25,06; -14,35</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>134,92; 319,4</t>
+          <t>136,26; 337,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>88,28; 252,0</t>
+          <t>88,66; 249,41</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-82,96; -45,94</t>
+          <t>-83,18; -46,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>103,54; 244,7</t>
+          <t>103,96; 242,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>58,3; 170,81</t>
+          <t>63,59; 171,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-87,58; -56,68</t>
+          <t>-88,0; -56,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>132,35; 241,34</t>
+          <t>132,35; 242,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>85,72; 177,15</t>
+          <t>87,77; 175,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,35; -58,92</t>
+          <t>-82,45; -59,23</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>41,05; 60,87</t>
+          <t>40,99; 60,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>47,29; 64,88</t>
+          <t>47,35; 65,18</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>30,66; 50,51</t>
+          <t>30,99; 51,13</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43,15; 61,07</t>
+          <t>43,27; 61,78</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>47,59; 64,14</t>
+          <t>48,0; 64,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>33,33; 53,66</t>
+          <t>35,25; 54,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,44</t>
+          <t>45,83; 58,67</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>50,34; 62,5</t>
+          <t>50,91; 62,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>35,89; 50,19</t>
+          <t>36,1; 49,63</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>88,35; 197,33</t>
+          <t>84,99; 194,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>99,35; 204,79</t>
+          <t>99,78; 207,46</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>66,19; 156,46</t>
+          <t>66,82; 157,46</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>97,64; 204,61</t>
+          <t>97,78; 212,82</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>107,6; 220,03</t>
+          <t>107,64; 216,09</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>76,75; 182,34</t>
+          <t>81,65; 181,25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>101,95; 176,52</t>
+          <t>106,87; 179,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>115,07; 191,06</t>
+          <t>118,34; 194,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>83,2; 153,17</t>
+          <t>85,8; 151,46</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>46,51; 55,17</t>
+          <t>46,57; 55,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>31,47; 40,94</t>
+          <t>31,62; 41,35</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,0</t>
+          <t>-6,9; 4,15</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49,08; 57,45</t>
+          <t>48,94; 57,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,83</t>
+          <t>34,55; 44,17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,47</t>
+          <t>-0,74; 8,84</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,15; 55,11</t>
+          <t>49,2; 55,04</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>34,83; 41,33</t>
+          <t>34,7; 41,13</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,52</t>
+          <t>-1,92; 5,43</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>134,61; 191,51</t>
+          <t>132,73; 193,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>91,9; 141,24</t>
+          <t>91,34; 144,81</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 13,64</t>
+          <t>-20,11; 14,21</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>147,63; 211,23</t>
+          <t>147,56; 210,6</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>106,73; 158,7</t>
+          <t>105,35; 160,46</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 33,79</t>
+          <t>-1,94; 31,66</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>150,17; 191,79</t>
+          <t>148,36; 189,84</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>106,02; 143,69</t>
+          <t>104,85; 141,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 18,81</t>
+          <t>-5,99; 18,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,52; 56,8</t>
+          <t>29,36; 56,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 29,59</t>
+          <t>-3,4; 29,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,38; -7,18</t>
+          <t>-42,98; -6,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,85; 56,43</t>
+          <t>27,41; 57,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 49,18</t>
+          <t>21,23; 51,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,69; -20,3</t>
+          <t>-44,89; -20,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,36; 52,7</t>
+          <t>32,48; 52,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,24; 36,27</t>
+          <t>14,69; 36,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-40,23; -16,86</t>
+          <t>-40,25; -17,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,02; 152,12</t>
+          <t>52,4; 152,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 73,78</t>
+          <t>-6,5; 72,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,08; -5,41</t>
+          <t>-80,32; -12,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,32; 179,14</t>
+          <t>52,96; 183,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,87; 150,44</t>
+          <t>41,69; 167,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,41; -59,29</t>
+          <t>-89,37; -59,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,17; 141,21</t>
+          <t>62,45; 142,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,54; 96,92</t>
+          <t>27,66; 96,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,12; -38,99</t>
+          <t>-80,76; -36,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,27; 55,09</t>
+          <t>30,19; 55,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 16,49</t>
+          <t>-10,52; 16,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -5,32</t>
+          <t>-28,92; -5,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,56; 69,09</t>
+          <t>45,79; 68,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 31,4</t>
+          <t>5,97; 29,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 10,65</t>
+          <t>-9,85; 11,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,71; 58,46</t>
+          <t>40,8; 59,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 18,77</t>
+          <t>1,29; 18,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,99; -0,04</t>
+          <t>-17,35; -0,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,52; 238,03</t>
+          <t>80,34; 236,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 68,67</t>
+          <t>-28,23; 61,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,19; -24,26</t>
+          <t>-78,07; -23,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159,35; 479,07</t>
+          <t>157,76; 479,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,86; 211,97</t>
+          <t>20,0; 199,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 71,44</t>
+          <t>-37,79; 74,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>129,97; 276,97</t>
+          <t>127,82; 281,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 88,71</t>
+          <t>4,41; 87,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,08; -1,63</t>
+          <t>-57,08; -0,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,95; 62,07</t>
+          <t>36,55; 62,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 27,55</t>
+          <t>-0,8; 28,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -0,73</t>
+          <t>-24,38; -1,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,02; 61,26</t>
+          <t>37,4; 62,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 26,09</t>
+          <t>-0,11; 25,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 1,9</t>
+          <t>-18,59; 3,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,42; 58,09</t>
+          <t>40,18; 58,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 24,23</t>
+          <t>4,17; 23,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -2,21</t>
+          <t>-18,71; -1,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,73; 279,63</t>
+          <t>98,43; 284,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 117,3</t>
+          <t>-2,32; 122,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,29; -0,7</t>
+          <t>-67,13; -2,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>113,49; 337,05</t>
+          <t>118,65; 338,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 136,25</t>
+          <t>-3,53; 130,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,33; 11,19</t>
+          <t>-60,46; 19,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119,44; 254,96</t>
+          <t>123,11; 268,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15,23; 106,6</t>
+          <t>11,44; 105,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,61; -9,28</t>
+          <t>-59,4; -7,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,72; 76,46</t>
+          <t>56,17; 75,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30,03; 56,47</t>
+          <t>29,54; 57,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,77; 17,4</t>
+          <t>-10,23; 16,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,92; 76,12</t>
+          <t>55,79; 75,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,95; 61,86</t>
+          <t>35,37; 62,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 43,44</t>
+          <t>4,86; 40,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,22; 73,65</t>
+          <t>60,02; 73,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37,31; 55,63</t>
+          <t>36,17; 56,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 27,22</t>
+          <t>2,5; 26,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>140,15; 350,66</t>
+          <t>139,96; 333,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,65; 247,71</t>
+          <t>78,97; 241,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 72,78</t>
+          <t>-28,42; 65,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154,09; 377,81</t>
+          <t>143,12; 345,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>100,69; 285,78</t>
+          <t>96,98; 286,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,63; 184,17</t>
+          <t>12,24; 180,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>164,44; 302,39</t>
+          <t>165,1; 305,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>105,37; 222,81</t>
+          <t>102,43; 232,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,21; 103,15</t>
+          <t>5,97; 101,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,32; 73,57</t>
+          <t>16,46; 74,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35,69; 85,77</t>
+          <t>34,33; 85,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,71; 15,62</t>
+          <t>-38,63; 13,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,4; 82,9</t>
+          <t>36,26; 84,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38,29; 87,15</t>
+          <t>43,22; 87,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 26,46</t>
+          <t>-29,89; 23,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,04; 74,5</t>
+          <t>36,56; 73,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>45,84; 81,95</t>
+          <t>46,89; 80,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 12,71</t>
+          <t>-23,89; 14,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25,48; 533,29</t>
+          <t>26,6; 555,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>57,55; 642,39</t>
+          <t>55,66; 642,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 132,33</t>
+          <t>-68,83; 93,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63,28; 688,25</t>
+          <t>62,88; 690,56</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>68,37; 706,09</t>
+          <t>78,22; 729,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 200,08</t>
+          <t>-53,76; 192,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,89; 462,89</t>
+          <t>76,61; 442,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>87,32; 503,27</t>
+          <t>92,33; 437,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 67,74</t>
+          <t>-49,28; 72,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>36,01; 64,01</t>
+          <t>34,53; 64,37</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20,16; 57,09</t>
+          <t>21,65; 59,17</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 24,76</t>
+          <t>-3,68; 24,58</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37,41; 63,3</t>
+          <t>37,63; 65,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,18; 63,76</t>
+          <t>30,66; 62,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 28,44</t>
+          <t>-2,13; 26,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,7; 60,45</t>
+          <t>40,85; 60,6</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>33,9; 57,36</t>
+          <t>31,8; 56,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 21,57</t>
+          <t>2,57; 22,94</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>123,84; 489,13</t>
+          <t>114,39; 478,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>72,36; 384,19</t>
+          <t>73,33; 407,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 172,21</t>
+          <t>-15,61; 168,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>103,01; 316,1</t>
+          <t>103,2; 330,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85,11; 319,88</t>
+          <t>89,36; 310,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 128,92</t>
+          <t>-5,61; 130,95</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>123,2; 302,06</t>
+          <t>129,89; 307,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>113,24; 293,63</t>
+          <t>110,02; 300,22</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,46; 108,94</t>
+          <t>7,75; 118,18</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>40,42; 59,61</t>
+          <t>41,49; 60,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27,25; 46,67</t>
+          <t>26,49; 46,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,67; -8,98</t>
+          <t>-25,28; -9,76</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37,58; 56,23</t>
+          <t>38,21; 56,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>21,25; 40,56</t>
+          <t>21,62; 42,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-31,4; -15,01</t>
+          <t>-30,75; -14,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,91; 55,67</t>
+          <t>42,59; 56,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>27,64; 41,03</t>
+          <t>27,24; 41,4</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-25,06; -14,35</t>
+          <t>-25,85; -13,91</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>136,26; 337,01</t>
+          <t>136,2; 316,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>88,66; 249,41</t>
+          <t>89,82; 246,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-83,18; -46,04</t>
+          <t>-83,76; -46,26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>103,96; 242,42</t>
+          <t>104,48; 237,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>63,59; 171,59</t>
+          <t>61,56; 179,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-88,0; -56,06</t>
+          <t>-87,07; -56,42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>132,35; 242,47</t>
+          <t>136,59; 248,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>87,77; 175,59</t>
+          <t>88,22; 180,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,45; -59,23</t>
+          <t>-82,47; -58,35</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>40,99; 60,89</t>
+          <t>42,8; 61,05</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>47,35; 65,18</t>
+          <t>47,69; 64,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>30,99; 51,13</t>
+          <t>29,93; 50,71</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43,27; 61,78</t>
+          <t>43,36; 61,16</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>48,0; 64,53</t>
+          <t>47,42; 64,45</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,25; 54,17</t>
+          <t>35,05; 54,79</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>45,83; 58,67</t>
+          <t>45,36; 58,33</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>50,91; 62,32</t>
+          <t>49,93; 62,25</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>36,1; 49,63</t>
+          <t>34,94; 49,41</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>84,99; 194,89</t>
+          <t>92,1; 193,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>99,78; 207,46</t>
+          <t>102,75; 208,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>66,82; 157,46</t>
+          <t>63,61; 156,5</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>97,78; 212,82</t>
+          <t>99,52; 210,03</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>107,64; 216,09</t>
+          <t>106,07; 222,89</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>81,65; 181,25</t>
+          <t>82,27; 185,43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>106,87; 179,78</t>
+          <t>104,56; 180,18</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>118,34; 194,39</t>
+          <t>114,73; 191,33</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>85,8; 151,46</t>
+          <t>80,73; 148,9</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>46,57; 55,47</t>
+          <t>46,41; 55,89</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>31,62; 41,35</t>
+          <t>31,65; 41,27</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 4,15</t>
+          <t>-6,32; 4,04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>48,94; 57,36</t>
+          <t>49,61; 57,63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>34,55; 44,17</t>
+          <t>34,79; 43,89</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,84</t>
+          <t>-0,65; 8,85</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,2; 55,04</t>
+          <t>49,4; 55,03</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,13</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,43</t>
+          <t>-1,66; 5,66</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>132,73; 193,69</t>
+          <t>134,55; 195,41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>91,34; 144,81</t>
+          <t>89,73; 141,25</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 14,21</t>
+          <t>-18,89; 13,79</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>147,56; 210,6</t>
+          <t>148,1; 207,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>105,35; 160,46</t>
+          <t>107,23; 158,95</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 31,66</t>
+          <t>-2,1; 31,79</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>148,36; 189,84</t>
+          <t>149,52; 190,04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>104,85; 141,51</t>
+          <t>106,43; 144,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 18,29</t>
+          <t>-5,06; 19,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43,67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35,78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-31,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>44,18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,84</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-28,47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>35,78</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-31,7</t>
+          <t>-35,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-30,16</t>
+          <t>-33,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,36; 56,69</t>
+          <t>28,63; 58,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 29,61</t>
+          <t>20,94; 49,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,98; -6,41</t>
+          <t>-43,73; -18,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,41; 57,9</t>
+          <t>30,3; 57,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,23; 51,15</t>
+          <t>-3,49; 28,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,89; -20,28</t>
+          <t>-47,46; -20,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,48; 52,98</t>
+          <t>32,11; 53,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 36,8</t>
+          <t>14,42; 37,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-40,25; -17,8</t>
+          <t>-42,73; -24,59</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>106,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-76,31%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>91,44%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>28,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-58,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>106,56%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-77,34%</t>
+          <t>-73,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-67,75%</t>
+          <t>-74,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,4; 152,98</t>
+          <t>58,09; 196,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 72,12</t>
+          <t>41,76; 160,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,32; -12,78</t>
+          <t>-88,7; -55,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,96; 183,16</t>
+          <t>53,58; 154,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,69; 167,92</t>
+          <t>-5,64; 75,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,37; -59,11</t>
+          <t>-85,51; -50,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,45; 142,8</t>
+          <t>63,28; 139,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,66; 96,43</t>
+          <t>28,88; 98,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,76; -36,61</t>
+          <t>-84,88; -62,25</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>58,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17,9</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>43,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,73</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-16,58</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,9</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>-13,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,16</t>
+          <t>-6,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,19; 55,23</t>
+          <t>46,55; 69,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 16,23</t>
+          <t>5,89; 30,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,92; -5,41</t>
+          <t>-10,07; 9,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,79; 68,68</t>
+          <t>29,71; 55,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 29,95</t>
+          <t>-10,14; 15,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 11,01</t>
+          <t>-24,5; -2,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,8; 59,09</t>
+          <t>41,36; 59,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 18,71</t>
+          <t>0,92; 18,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -0,13</t>
+          <t>-14,23; 1,21</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>278,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>85,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-0,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>139,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-53,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>278,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>85,28%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>-43,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,38%</t>
+          <t>-25,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,34; 236,95</t>
+          <t>163,7; 492,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 61,61</t>
+          <t>20,63; 191,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,07; -23,47</t>
+          <t>-38,88; 62,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157,76; 479,67</t>
+          <t>77,88; 254,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 199,38</t>
+          <t>-27,36; 66,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 74,95</t>
+          <t>-65,81; -8,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>127,82; 281,2</t>
+          <t>132,04; 276,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 87,96</t>
+          <t>2,82; 87,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,08; -0,58</t>
+          <t>-46,43; 7,1</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49,92</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,13</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,28</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>49,84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>14,38</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-12,89</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>49,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,91</t>
+          <t>-12,83</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,33</t>
+          <t>-10,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,55; 62,52</t>
+          <t>36,39; 61,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 28,32</t>
+          <t>0,34; 25,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,38; -1,1</t>
+          <t>-19,19; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37,4; 62,43</t>
+          <t>36,56; 62,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 25,78</t>
+          <t>-0,39; 28,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 3,14</t>
+          <t>-25,52; -0,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,18; 58,26</t>
+          <t>39,31; 58,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 23,9</t>
+          <t>5,01; 23,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,71; -1,64</t>
+          <t>-18,72; -2,66</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>201,11%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-33,36%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>168,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>48,71%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-43,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>201,11%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-31,87%</t>
+          <t>-43,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-38,09%</t>
+          <t>-38,72%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98,43; 284,82</t>
+          <t>113,71; 335,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 122,48</t>
+          <t>0,95; 127,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,13; -2,8</t>
+          <t>-63,64; 13,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118,65; 338,58</t>
+          <t>96,66; 292,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 130,89</t>
+          <t>-2,77; 127,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 19,45</t>
+          <t>-69,47; 0,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>123,11; 268,94</t>
+          <t>118,5; 261,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,44; 105,91</t>
+          <t>14,65; 102,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,4; -7,56</t>
+          <t>-57,4; -7,47</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67,16</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21,34</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>66,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>44,13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>67,16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>50,22</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,18</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13,17</t>
+          <t>12,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>56,17; 75,53</t>
+          <t>56,04; 75,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,54; 57,41</t>
+          <t>36,82; 61,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 16,31</t>
+          <t>5,74; 41,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,79; 75,85</t>
+          <t>55,92; 76,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,37; 62,24</t>
+          <t>29,54; 57,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 40,72</t>
+          <t>-10,22; 16,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,02; 73,25</t>
+          <t>59,34; 73,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36,17; 56,23</t>
+          <t>37,88; 57,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 26,03</t>
+          <t>0,8; 24,49</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>229,09%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>171,3%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>72,8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>217,44%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>143,65%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>229,09%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>171,3%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>139,96; 333,1</t>
+          <t>145,94; 339,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,97; 241,78</t>
+          <t>103,43; 263,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 65,03</t>
+          <t>12,22; 179,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>143,12; 345,65</t>
+          <t>134,61; 344,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>96,98; 286,49</t>
+          <t>80,5; 261,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,24; 180,42</t>
+          <t>-27,86; 68,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>165,1; 305,17</t>
+          <t>160,44; 301,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>102,43; 232,32</t>
+          <t>106,27; 228,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 101,68</t>
+          <t>0,74; 94,29</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>61,12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67,5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,54</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>48,74</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>63,81</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,47</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61,12</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>67,5</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>-8,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-3,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>16,46; 74,65</t>
+          <t>33,5; 82,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34,33; 85,27</t>
+          <t>41,4; 87,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-38,63; 13,56</t>
+          <t>-27,83; 23,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36,26; 84,87</t>
+          <t>16,61; 75,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43,22; 87,71</t>
+          <t>35,2; 85,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 23,89</t>
+          <t>-35,05; 16,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,56; 73,6</t>
+          <t>36,25; 74,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46,89; 80,36</t>
+          <t>46,31; 81,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 14,19</t>
+          <t>-22,46; 15,31</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>198,58%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>219,33%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>142,34%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>186,33%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-27,64%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>198,58%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>219,33%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>-25,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-9,0%</t>
+          <t>-11,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26,6; 555,56</t>
+          <t>60,02; 674,97</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55,66; 642,53</t>
+          <t>74,17; 724,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 93,79</t>
+          <t>-55,84; 210,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62,88; 690,56</t>
+          <t>27,62; 568,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>78,22; 729,99</t>
+          <t>55,89; 634,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 192,22</t>
+          <t>-66,35; 118,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,61; 442,37</t>
+          <t>74,77; 490,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>92,33; 437,55</t>
+          <t>89,82; 501,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 72,96</t>
+          <t>-48,03; 100,26</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>52,01</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>49,22</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11,55</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>50,42</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>40,41</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>10,56</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>52,01</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>49,22</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,18</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,13</t>
+          <t>9,73</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>34,53; 64,37</t>
+          <t>36,59; 64,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>21,65; 59,17</t>
+          <t>32,5; 64,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 24,58</t>
+          <t>-1,46; 25,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37,63; 65,79</t>
+          <t>34,24; 64,14</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>30,66; 62,12</t>
+          <t>22,33; 57,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 26,37</t>
+          <t>-5,93; 21,7</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,85; 60,6</t>
+          <t>39,37; 59,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>31,8; 56,69</t>
+          <t>32,71; 56,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,57; 22,94</t>
+          <t>-0,49; 19,8</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>184,34%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>174,43%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>233,12%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>186,81%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>48,82%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>184,34%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>174,43%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>114,39; 478,49</t>
+          <t>104,28; 327,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>73,33; 407,1</t>
+          <t>90,22; 325,18</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 168,75</t>
+          <t>-5,41; 119,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>103,2; 330,69</t>
+          <t>112,61; 453,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>89,36; 310,17</t>
+          <t>70,68; 387,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 130,95</t>
+          <t>-21,59; 148,58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>129,89; 307,36</t>
+          <t>127,45; 305,29</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>110,02; 300,22</t>
+          <t>103,71; 279,53</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,75; 118,18</t>
+          <t>-1,82; 97,82</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>47,0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>31,61</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-22,69</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>51,01</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>37,06</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-16,79</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>47,0</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>31,61</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-22,67</t>
+          <t>-16,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-19,74</t>
+          <t>-19,63</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>41,49; 60,06</t>
+          <t>37,1; 56,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>26,49; 46,99</t>
+          <t>20,54; 41,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-25,28; -9,76</t>
+          <t>-31,66; -14,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38,21; 56,05</t>
+          <t>41,38; 59,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>21,62; 42,41</t>
+          <t>25,94; 46,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-30,75; -14,43</t>
+          <t>-24,0; -9,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,59; 56,07</t>
+          <t>42,48; 55,64</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>27,24; 41,4</t>
+          <t>26,65; 41,18</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-25,85; -13,91</t>
+          <t>-25,54; -13,62</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>156,45%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>105,22%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-75,53%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>209,41%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>152,16%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-68,94%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>156,45%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>105,22%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-75,45%</t>
+          <t>-67,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-72,57%</t>
+          <t>-72,16%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>136,2; 316,82</t>
+          <t>103,54; 244,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>89,82; 246,71</t>
+          <t>58,3; 170,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-83,76; -46,26</t>
+          <t>-87,01; -55,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>104,48; 237,96</t>
+          <t>134,92; 319,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>61,56; 179,75</t>
+          <t>88,28; 252,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-87,07; -56,42</t>
+          <t>-82,84; -44,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>136,59; 248,07</t>
+          <t>132,35; 241,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>88,22; 180,0</t>
+          <t>85,72; 177,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -58,35</t>
+          <t>-82,25; -57,22</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>52,76</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>56,05</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>44,33</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>51,47</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>56,63</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>41,28</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>52,76</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>56,05</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,61</t>
+          <t>40,14</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>43,02</t>
+          <t>42,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>42,8; 61,05</t>
+          <t>43,15; 61,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>47,69; 64,8</t>
+          <t>47,59; 64,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>29,93; 50,71</t>
+          <t>32,88; 53,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43,36; 61,16</t>
+          <t>41,05; 60,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>47,42; 64,45</t>
+          <t>47,29; 64,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>35,05; 54,79</t>
+          <t>29,14; 49,93</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>45,36; 58,33</t>
+          <t>44,95; 58,44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>49,93; 62,25</t>
+          <t>50,34; 62,5</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>34,94; 49,41</t>
+          <t>35,02; 49,63</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>143,57%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>152,52%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>120,63%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>130,97%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>144,1%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>105,04%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>143,57%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>152,52%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>121,39%</t>
+          <t>102,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>113,27%</t>
+          <t>111,46%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>92,1; 193,38</t>
+          <t>97,64; 204,61</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>102,75; 208,03</t>
+          <t>107,6; 220,03</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>63,61; 156,5</t>
+          <t>76,03; 180,56</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>99,52; 210,03</t>
+          <t>88,35; 197,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>106,07; 222,89</t>
+          <t>99,35; 204,79</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>82,27; 185,43</t>
+          <t>64,2; 152,45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>104,56; 180,18</t>
+          <t>101,95; 176,52</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>114,73; 191,33</t>
+          <t>115,07; 191,06</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>80,73; 148,9</t>
+          <t>81,4; 151,09</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>53,3</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>39,45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>50,96</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>36,4</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>53,3</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>39,45</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>46,41; 55,89</t>
+          <t>49,08; 57,45</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>31,65; 41,27</t>
+          <t>34,91; 43,83</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,04</t>
+          <t>0,54; 10,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,63</t>
+          <t>46,51; 55,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,89</t>
+          <t>31,47; 40,94</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,85</t>
+          <t>-3,97; 5,0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,4; 55,03</t>
+          <t>49,15; 55,11</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,83; 41,33</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,66</t>
+          <t>-0,38; 6,52</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>176,04%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>130,28%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>161,23%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>115,17%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>176,04%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>130,28%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>134,55; 195,41</t>
+          <t>147,63; 211,23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>89,73; 141,25</t>
+          <t>106,73; 158,7</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 13,79</t>
+          <t>1,64; 37,37</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>148,1; 207,39</t>
+          <t>134,61; 191,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>107,23; 158,95</t>
+          <t>91,9; 141,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 31,79</t>
+          <t>-11,49; 17,22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>149,52; 190,04</t>
+          <t>150,17; 191,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>106,43; 144,43</t>
+          <t>106,02; 143,69</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 19,6</t>
+          <t>-1,18; 22,1</t>
         </is>
       </c>
     </row>
